--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_auto_truck.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-12.4</v>
+        <v>-40.7</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +612,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>211.9</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.09517179429598024</v>
+      </c>
+      <c r="W2">
+        <v>0.7752380952380953</v>
       </c>
       <c r="X2">
-        <v>0.1092213732321282</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-39.20579078573027</v>
+        <v>0.09334649757714289</v>
+      </c>
+      <c r="Y2">
+        <v>0.6818915976609524</v>
       </c>
       <c r="AB2">
-        <v>0.1092180473201509</v>
-      </c>
-      <c r="AC2">
-        <v>-39.31500883305042</v>
+        <v>0.09274812651170021</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="AE2">
-        <v>0.2695240831739793</v>
+        <v>5.228989464894966</v>
       </c>
       <c r="AF2">
-        <v>0.2695240831739793</v>
+        <v>27.42898946489496</v>
       </c>
       <c r="AG2">
-        <v>0.2695240831739793</v>
+        <v>-184.4710105351051</v>
       </c>
       <c r="AH2">
-        <v>7.493921120367762e-05</v>
+        <v>0.01216941154450783</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>0.08974603329650933</v>
       </c>
       <c r="AJ2">
-        <v>7.493921120367762e-05</v>
+        <v>-0.09033711641059752</v>
       </c>
       <c r="AK2">
-        <v>1</v>
+        <v>-1.968131861745895</v>
       </c>
       <c r="AL2">
-        <v>1.98</v>
+        <v>0.037</v>
       </c>
       <c r="AM2">
-        <v>1.98</v>
+        <v>0.037</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.5721649484536083</v>
       </c>
       <c r="AO2">
-        <v>-5.454545454545455</v>
+        <v>-1091.891891891892</v>
       </c>
       <c r="AP2">
-        <v>-0.02563721898354222</v>
+        <v>4.754407488018172</v>
       </c>
       <c r="AQ2">
-        <v>-5.454545454545455</v>
+        <v>-1091.891891891892</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +689,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-12.4</v>
+        <v>-40.7</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +713,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>211.9</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.09517179429598024</v>
+      </c>
+      <c r="W3">
+        <v>0.7752380952380953</v>
       </c>
       <c r="X3">
-        <v>0.1092213732321282</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-39.20579078573027</v>
+        <v>0.09334649757714289</v>
+      </c>
+      <c r="Y3">
+        <v>0.6818915976609524</v>
       </c>
       <c r="AB3">
-        <v>0.1092180473201509</v>
-      </c>
-      <c r="AC3">
-        <v>-39.31500883305042</v>
+        <v>0.09274812651170021</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="AE3">
-        <v>0.2695240831739793</v>
+        <v>5.228989464894966</v>
       </c>
       <c r="AF3">
-        <v>0.2695240831739793</v>
+        <v>27.42898946489496</v>
       </c>
       <c r="AG3">
-        <v>0.2695240831739793</v>
+        <v>-184.4710105351051</v>
       </c>
       <c r="AH3">
-        <v>7.493921120367762e-05</v>
+        <v>0.01216941154450783</v>
       </c>
       <c r="AI3">
-        <v>1</v>
+        <v>0.08974603329650933</v>
       </c>
       <c r="AJ3">
-        <v>7.493921120367762e-05</v>
+        <v>-0.09033711641059752</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>-1.968131861745895</v>
       </c>
       <c r="AL3">
-        <v>1.98</v>
+        <v>0.037</v>
       </c>
       <c r="AM3">
-        <v>1.98</v>
+        <v>0.037</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.5721649484536083</v>
       </c>
       <c r="AO3">
-        <v>-5.454545454545455</v>
+        <v>-1091.891891891892</v>
       </c>
       <c r="AP3">
-        <v>-0.02563721898354222</v>
+        <v>4.754407488018172</v>
       </c>
       <c r="AQ3">
-        <v>-5.454545454545455</v>
+        <v>-1091.891891891892</v>
       </c>
     </row>
   </sheetData>
